--- a/output/AGA_Gap_Analysis.xlsx
+++ b/output/AGA_Gap_Analysis.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,27 +417,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>compound</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>target_importance</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>compound_importance</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>gap_score</t>
         </is>

--- a/output/AGA_Gap_Analysis.xlsx
+++ b/output/AGA_Gap_Analysis.xlsx
@@ -479,10 +479,10 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E3" t="n">
-        <v>2205</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>2100</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="5">
@@ -824,22 +824,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>Dermal papilla cells</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>611</v>
+        <v>620</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -866,49 +866,49 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dutasteride</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="D22" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
-        <v>592</v>
+        <v>611</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Caspase-3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>Dutasteride</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="E23" t="n">
-        <v>576</v>
+        <v>592</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -929,22 +929,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E25" t="n">
-        <v>564</v>
+        <v>576</v>
       </c>
     </row>
     <row r="26">
@@ -955,7 +955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -971,22 +971,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dermal papilla cells</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>558</v>
+        <v>564</v>
       </c>
     </row>
     <row r="28">
@@ -997,7 +997,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1937,43 +1937,43 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D73" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E73" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D74" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E74" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="75">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -2000,12 +2000,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -2042,22 +2042,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D78" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E78" t="n">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="79">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2630,19 +2630,19 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D106" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E106" t="n">
         <v>180</v>
@@ -2651,19 +2651,19 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D107" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E107" t="n">
         <v>180</v>
@@ -2672,49 +2672,49 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D108" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E108" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D109" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E109" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2735,7 +2735,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2756,106 +2756,106 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D112" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E112" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D113" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E113" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D114" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E114" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D115" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E115" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D116" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E116" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="117">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2945,12 +2945,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -3239,19 +3239,19 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C135" t="n">
+        <v>15</v>
+      </c>
+      <c r="D135" t="n">
         <v>10</v>
-      </c>
-      <c r="D135" t="n">
-        <v>15</v>
       </c>
       <c r="E135" t="n">
         <v>150</v>
@@ -3260,7 +3260,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3281,40 +3281,40 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D137" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E137" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D138" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E138" t="n">
         <v>144</v>
@@ -3323,7 +3323,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3344,7 +3344,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3365,7 +3365,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3386,28 +3386,28 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D142" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E142" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3428,40 +3428,40 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D144" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E144" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C145" t="n">
+        <v>14</v>
+      </c>
+      <c r="D145" t="n">
         <v>10</v>
-      </c>
-      <c r="D145" t="n">
-        <v>14</v>
       </c>
       <c r="E145" t="n">
         <v>140</v>
@@ -3470,7 +3470,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3491,7 +3491,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3512,43 +3512,43 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D148" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E148" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D149" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E149" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="150">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -3617,19 +3617,19 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D153" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E153" t="n">
         <v>135</v>
@@ -3638,7 +3638,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3659,40 +3659,40 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D155" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E155" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C156" t="n">
+        <v>13</v>
+      </c>
+      <c r="D156" t="n">
         <v>10</v>
-      </c>
-      <c r="D156" t="n">
-        <v>13</v>
       </c>
       <c r="E156" t="n">
         <v>130</v>
@@ -3701,19 +3701,19 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C157" t="n">
+        <v>13</v>
+      </c>
+      <c r="D157" t="n">
         <v>10</v>
-      </c>
-      <c r="D157" t="n">
-        <v>13</v>
       </c>
       <c r="E157" t="n">
         <v>130</v>
@@ -3722,12 +3722,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -3743,12 +3743,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -3764,12 +3764,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -3785,85 +3785,85 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D161" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E161" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D162" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E162" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D163" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E163" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Caspase-3</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D164" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E164" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="165">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3932,19 +3932,19 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D168" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E168" t="n">
         <v>126</v>
@@ -3953,19 +3953,19 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D169" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E169" t="n">
         <v>126</v>
@@ -3974,12 +3974,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3995,61 +3995,61 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D171" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E171" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D172" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E172" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D173" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E173" t="n">
         <v>120</v>
@@ -4058,7 +4058,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4079,7 +4079,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4100,7 +4100,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4121,7 +4121,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4142,43 +4142,43 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D178" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E178" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D179" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E179" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="180">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -4226,12 +4226,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -4835,70 +4835,70 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D211" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E211" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D212" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E212" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D213" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E213" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4919,106 +4919,106 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D215" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E215" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D216" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E216" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D217" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E217" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Caspase-3</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D218" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E218" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Caspase-3</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D219" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E219" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="220">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -5066,12 +5066,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -5087,12 +5087,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -5171,12 +5171,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -5276,49 +5276,49 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D232" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E232" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C233" t="n">
         <v>9</v>
       </c>
       <c r="D233" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E233" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5330,52 +5330,52 @@
         <v>9</v>
       </c>
       <c r="D234" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E234" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C235" t="n">
         <v>9</v>
       </c>
       <c r="D235" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E235" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>Caspase-3</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D236" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E236" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="237">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -5402,12 +5402,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -5423,12 +5423,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -5444,12 +5444,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -5528,12 +5528,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -5549,12 +5549,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -5654,12 +5654,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -5822,28 +5822,28 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>Caspase-3</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D258" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E258" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5864,7 +5864,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5885,7 +5885,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5906,19 +5906,19 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C262" t="n">
+        <v>9</v>
+      </c>
+      <c r="D262" t="n">
         <v>8</v>
-      </c>
-      <c r="D262" t="n">
-        <v>9</v>
       </c>
       <c r="E262" t="n">
         <v>72</v>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C264" t="n">

--- a/output/AGA_Gap_Analysis.xlsx
+++ b/output/AGA_Gap_Analysis.xlsx
@@ -479,10 +479,10 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E3" t="n">
-        <v>2214</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="4">
@@ -539,13 +539,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
         <v>74</v>
       </c>
       <c r="E6" t="n">
-        <v>1332</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="7">
@@ -887,49 +887,49 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dutasteride</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D23" t="n">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="E23" t="n">
-        <v>592</v>
+        <v>608</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Caspase-3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>Dutasteride</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="E24" t="n">
-        <v>576</v>
+        <v>592</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1307,22 +1307,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D43" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="E43" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="44">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1349,22 +1349,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D45" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E45" t="n">
-        <v>336</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1391,22 +1391,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D47" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E47" t="n">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="48">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1433,22 +1433,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D49" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E49" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="50">
@@ -1517,22 +1517,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D53" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E53" t="n">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="54">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1559,28 +1559,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D55" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E55" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1685,49 +1685,49 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D61" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E61" t="n">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D62" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E62" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1748,43 +1748,43 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D64" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E64" t="n">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>Caspase-3</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D65" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="E65" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="66">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1874,19 +1874,19 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D70" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E70" t="n">
         <v>252</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1916,12 +1916,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1958,70 +1958,70 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D74" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E74" t="n">
-        <v>240</v>
+        <v>247</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D75" t="n">
         <v>13</v>
       </c>
       <c r="E75" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D76" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E76" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2042,7 +2042,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2063,43 +2063,43 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D79" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E79" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D80" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E80" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="81">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2147,91 +2147,91 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D83" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E83" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D84" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E84" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D85" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E85" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D86" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E86" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2252,7 +2252,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2315,28 +2315,28 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D91" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E91" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2357,49 +2357,49 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D93" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E93" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D94" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E94" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2504,22 +2504,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D100" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E100" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="101">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2546,19 +2546,19 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D102" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E102" t="n">
         <v>182</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2588,12 +2588,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2630,28 +2630,28 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D106" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E106" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2714,306 +2714,306 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D110" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E110" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D111" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E111" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D112" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E112" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D113" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E113" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D114" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E114" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D115" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E115" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D116" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E116" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D117" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E117" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D118" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E118" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D119" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E119" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D120" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E120" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D121" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E121" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D122" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E122" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D123" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E123" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -3029,12 +3029,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -3050,12 +3050,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -3071,49 +3071,49 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D127" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E127" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D128" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E128" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3134,22 +3134,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D130" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E130" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="131">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3176,12 +3176,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -3218,43 +3218,43 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D134" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E134" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D135" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E135" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="136">
@@ -3265,98 +3265,98 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D136" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E136" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D137" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E137" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D138" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E138" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D139" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E139" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D140" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E140" t="n">
         <v>144</v>
@@ -3365,7 +3365,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3386,7 +3386,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3407,85 +3407,85 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D143" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E143" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D144" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E144" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D145" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E145" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D146" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E146" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="147">
@@ -3496,56 +3496,56 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D147" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E147" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D148" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E148" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C149" t="n">
+        <v>14</v>
+      </c>
+      <c r="D149" t="n">
         <v>10</v>
-      </c>
-      <c r="D149" t="n">
-        <v>14</v>
       </c>
       <c r="E149" t="n">
         <v>140</v>
@@ -3554,43 +3554,43 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D150" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E150" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D151" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E151" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="152">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -3638,19 +3638,19 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D154" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E154" t="n">
         <v>135</v>
@@ -3659,19 +3659,19 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D155" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E155" t="n">
         <v>135</v>
@@ -3680,43 +3680,43 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D156" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E156" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D157" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E157" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="158">
@@ -3727,17 +3727,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D158" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E158" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="159">
@@ -3748,35 +3748,35 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D159" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E159" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C160" t="n">
+        <v>13</v>
+      </c>
+      <c r="D160" t="n">
         <v>10</v>
-      </c>
-      <c r="D160" t="n">
-        <v>13</v>
       </c>
       <c r="E160" t="n">
         <v>130</v>
@@ -3785,19 +3785,19 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C161" t="n">
+        <v>13</v>
+      </c>
+      <c r="D161" t="n">
         <v>10</v>
-      </c>
-      <c r="D161" t="n">
-        <v>13</v>
       </c>
       <c r="E161" t="n">
         <v>130</v>
@@ -3806,7 +3806,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3848,64 +3848,64 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D164" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E164" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D165" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E165" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Caspase-3</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D166" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E166" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="167">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3974,19 +3974,19 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D170" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E170" t="n">
         <v>126</v>
@@ -3995,19 +3995,19 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D171" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E171" t="n">
         <v>126</v>
@@ -4016,12 +4016,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -4037,43 +4037,43 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D173" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E173" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D174" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E174" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="175">
@@ -4084,35 +4084,35 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D175" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E175" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D176" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E176" t="n">
         <v>120</v>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -4142,12 +4142,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -4184,22 +4184,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D180" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E180" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="181">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -4247,12 +4247,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -4352,19 +4352,19 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D188" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E188" t="n">
         <v>117</v>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -4394,12 +4394,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -4436,12 +4436,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -4478,12 +4478,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -4520,40 +4520,40 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D196" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E196" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C197" t="n">
+        <v>14</v>
+      </c>
+      <c r="D197" t="n">
         <v>8</v>
-      </c>
-      <c r="D197" t="n">
-        <v>14</v>
       </c>
       <c r="E197" t="n">
         <v>112</v>
@@ -4562,40 +4562,40 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Caspase-3</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D198" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E198" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C199" t="n">
+        <v>11</v>
+      </c>
+      <c r="D199" t="n">
         <v>10</v>
-      </c>
-      <c r="D199" t="n">
-        <v>11</v>
       </c>
       <c r="E199" t="n">
         <v>110</v>
@@ -4604,7 +4604,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4625,22 +4625,22 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D201" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E201" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="202">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -4667,7 +4667,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4688,7 +4688,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4709,12 +4709,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -4751,28 +4751,28 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D207" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E207" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4793,19 +4793,19 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C209" t="n">
+        <v>13</v>
+      </c>
+      <c r="D209" t="n">
         <v>8</v>
-      </c>
-      <c r="D209" t="n">
-        <v>13</v>
       </c>
       <c r="E209" t="n">
         <v>104</v>
@@ -4819,7 +4819,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -4835,22 +4835,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Caspase-3</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D211" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E211" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="212">
@@ -4898,19 +4898,19 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D214" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E214" t="n">
         <v>99</v>
@@ -4919,19 +4919,19 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D215" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E215" t="n">
         <v>99</v>
@@ -4940,19 +4940,19 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D216" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E216" t="n">
         <v>99</v>
@@ -4961,19 +4961,19 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D217" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E217" t="n">
         <v>99</v>
@@ -4982,127 +4982,127 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D218" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E218" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D219" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E219" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D220" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E220" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D221" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E221" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Caspase-3</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D222" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E222" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Caspase-3</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D223" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E223" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="224">
@@ -5360,19 +5360,19 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C236" t="n">
+        <v>11</v>
+      </c>
+      <c r="D236" t="n">
         <v>8</v>
-      </c>
-      <c r="D236" t="n">
-        <v>11</v>
       </c>
       <c r="E236" t="n">
         <v>88</v>
@@ -5381,22 +5381,22 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>Caspase-3</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D237" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E237" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="238">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -5465,12 +5465,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -5570,12 +5570,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -5675,12 +5675,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -5759,22 +5759,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D255" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E255" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="256">

--- a/output/AGA_Gap_Analysis.xlsx
+++ b/output/AGA_Gap_Analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E268"/>
+  <dimension ref="A1:E267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,10 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E3" t="n">
-        <v>2223</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="4">
@@ -908,43 +908,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dutasteride</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D24" t="n">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="E24" t="n">
-        <v>592</v>
+        <v>576</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="D25" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>576</v>
+        <v>564</v>
       </c>
     </row>
     <row r="26">
@@ -955,7 +955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -971,22 +971,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>Dermal papilla cells</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>564</v>
+        <v>558</v>
       </c>
     </row>
     <row r="28">
@@ -997,7 +997,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1055,70 +1055,70 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dermal papilla cells</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>558</v>
+        <v>517</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>Dermal papilla cells</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>517</v>
+        <v>496</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dermal papilla cells</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E33" t="n">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1127,34 +1127,34 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
       </c>
       <c r="E34" t="n">
-        <v>480</v>
+        <v>448</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D35" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>448</v>
+        <v>423</v>
       </c>
     </row>
     <row r="36">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1181,148 +1181,148 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E37" t="n">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E38" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D39" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E39" t="n">
-        <v>400</v>
+        <v>392</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D40" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>392</v>
+        <v>376</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E41" t="n">
-        <v>376</v>
+        <v>364</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D42" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E42" t="n">
-        <v>364</v>
+        <v>352</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D43" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E43" t="n">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1349,22 +1349,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D45" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E45" t="n">
-        <v>350</v>
+        <v>336</v>
       </c>
     </row>
     <row r="46">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1391,22 +1391,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E47" t="n">
-        <v>336</v>
+        <v>325</v>
       </c>
     </row>
     <row r="48">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1433,28 +1433,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D49" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E49" t="n">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1475,64 +1475,64 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D51" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E51" t="n">
-        <v>320</v>
+        <v>308</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D52" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E52" t="n">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D53" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E53" t="n">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="54">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1559,40 +1559,40 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D55" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E55" t="n">
-        <v>300</v>
+        <v>288</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D56" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E56" t="n">
         <v>288</v>
@@ -1601,7 +1601,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1622,7 +1622,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1643,7 +1643,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1664,127 +1664,127 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D60" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E60" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D61" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E61" t="n">
-        <v>285</v>
+        <v>275</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D62" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E62" t="n">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D63" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E63" t="n">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D64" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E64" t="n">
-        <v>266</v>
+        <v>252</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D65" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E65" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="66">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1853,19 +1853,19 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D69" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E69" t="n">
         <v>252</v>
@@ -1874,19 +1874,19 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D70" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E70" t="n">
         <v>252</v>
@@ -1895,211 +1895,211 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D71" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E71" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D72" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E72" t="n">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D73" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E73" t="n">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D74" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E74" t="n">
-        <v>247</v>
+        <v>240</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D75" t="n">
         <v>13</v>
       </c>
       <c r="E75" t="n">
-        <v>247</v>
+        <v>234</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D76" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E76" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D77" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E77" t="n">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D78" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E78" t="n">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D79" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E79" t="n">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D80" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E80" t="n">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2147,313 +2147,313 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E83" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D84" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E84" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D85" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E85" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D86" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E86" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D87" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E87" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D88" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E88" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D89" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E89" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D90" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E90" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D91" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E91" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D92" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E92" t="n">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D93" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E93" t="n">
-        <v>208</v>
+        <v>198</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D94" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E94" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D95" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E95" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D96" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E96" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C97" t="n">
+        <v>13</v>
+      </c>
+      <c r="D97" t="n">
         <v>15</v>
-      </c>
-      <c r="D97" t="n">
-        <v>13</v>
       </c>
       <c r="E97" t="n">
         <v>195</v>
@@ -2462,82 +2462,82 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D98" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E98" t="n">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D99" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E99" t="n">
-        <v>195</v>
+        <v>182</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D100" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E100" t="n">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C101" t="n">
+        <v>13</v>
+      </c>
+      <c r="D101" t="n">
         <v>14</v>
-      </c>
-      <c r="D101" t="n">
-        <v>13</v>
       </c>
       <c r="E101" t="n">
         <v>182</v>
@@ -2546,19 +2546,19 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C102" t="n">
+        <v>13</v>
+      </c>
+      <c r="D102" t="n">
         <v>14</v>
-      </c>
-      <c r="D102" t="n">
-        <v>13</v>
       </c>
       <c r="E102" t="n">
         <v>182</v>
@@ -2567,7 +2567,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2588,7 +2588,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2609,61 +2609,61 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D105" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E105" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D106" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E106" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D107" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E107" t="n">
         <v>180</v>
@@ -2672,64 +2672,64 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D108" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E108" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D109" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E109" t="n">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D110" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E110" t="n">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="111">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2798,49 +2798,49 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D114" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E114" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D115" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E115" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2861,7 +2861,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2882,127 +2882,127 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D118" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E118" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D119" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E119" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D120" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E120" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D121" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E121" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D122" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E122" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D123" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E123" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="124">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -3071,91 +3071,91 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D127" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E127" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D128" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E128" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D129" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E129" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D130" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E130" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3176,7 +3176,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3197,61 +3197,61 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D133" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E133" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D134" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E134" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C135" t="n">
+        <v>11</v>
+      </c>
+      <c r="D135" t="n">
         <v>14</v>
-      </c>
-      <c r="D135" t="n">
-        <v>11</v>
       </c>
       <c r="E135" t="n">
         <v>154</v>
@@ -3260,103 +3260,103 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D136" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E136" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D137" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E137" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D138" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E138" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D139" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E139" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D140" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E140" t="n">
         <v>144</v>
@@ -3365,7 +3365,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3386,7 +3386,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3407,61 +3407,61 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D143" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E143" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D144" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E144" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D145" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E145" t="n">
         <v>143</v>
@@ -3470,19 +3470,19 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D146" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E146" t="n">
         <v>143</v>
@@ -3491,61 +3491,61 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D147" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E147" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D148" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E148" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C149" t="n">
+        <v>10</v>
+      </c>
+      <c r="D149" t="n">
         <v>14</v>
-      </c>
-      <c r="D149" t="n">
-        <v>10</v>
       </c>
       <c r="E149" t="n">
         <v>140</v>
@@ -3554,43 +3554,43 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D150" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E150" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D151" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E151" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="152">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -3638,19 +3638,19 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C154" t="n">
+        <v>9</v>
+      </c>
+      <c r="D154" t="n">
         <v>15</v>
-      </c>
-      <c r="D154" t="n">
-        <v>9</v>
       </c>
       <c r="E154" t="n">
         <v>135</v>
@@ -3659,19 +3659,19 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C155" t="n">
+        <v>9</v>
+      </c>
+      <c r="D155" t="n">
         <v>15</v>
-      </c>
-      <c r="D155" t="n">
-        <v>9</v>
       </c>
       <c r="E155" t="n">
         <v>135</v>
@@ -3680,7 +3680,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>5a-Reductase Type 2</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3701,22 +3701,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D157" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E157" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="158">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -3743,28 +3743,28 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D159" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E159" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3785,19 +3785,19 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D161" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E161" t="n">
         <v>130</v>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -3827,12 +3827,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -3869,43 +3869,43 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D165" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E165" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D166" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="167">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3974,19 +3974,19 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C170" t="n">
+        <v>9</v>
+      </c>
+      <c r="D170" t="n">
         <v>14</v>
-      </c>
-      <c r="D170" t="n">
-        <v>9</v>
       </c>
       <c r="E170" t="n">
         <v>126</v>
@@ -3995,19 +3995,19 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C171" t="n">
+        <v>9</v>
+      </c>
+      <c r="D171" t="n">
         <v>14</v>
-      </c>
-      <c r="D171" t="n">
-        <v>9</v>
       </c>
       <c r="E171" t="n">
         <v>126</v>
@@ -4016,12 +4016,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -4037,7 +4037,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>5a-Reductase Type 2</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4058,7 +4058,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>5a-Reductase Type 2</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4541,82 +4541,82 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>5a-Reductase Type 2</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D197" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E197" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>5a-Reductase Type 2</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D198" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E198" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D199" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E199" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C200" t="n">
+        <v>11</v>
+      </c>
+      <c r="D200" t="n">
         <v>10</v>
-      </c>
-      <c r="D200" t="n">
-        <v>11</v>
       </c>
       <c r="E200" t="n">
         <v>110</v>
@@ -4625,7 +4625,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4646,22 +4646,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D202" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E202" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="203">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -4688,7 +4688,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4709,7 +4709,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4730,12 +4730,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -4772,82 +4772,82 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D208" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E208" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>5a-Reductase Type 2</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D209" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E209" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>5a-Reductase Type 2</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D210" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E210" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C211" t="n">
+        <v>13</v>
+      </c>
+      <c r="D211" t="n">
         <v>8</v>
-      </c>
-      <c r="D211" t="n">
-        <v>13</v>
       </c>
       <c r="E211" t="n">
         <v>104</v>
@@ -4856,28 +4856,28 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D212" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E212" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4898,22 +4898,22 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D214" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E214" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="215">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -4982,19 +4982,19 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D218" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E218" t="n">
         <v>99</v>
@@ -5003,7 +5003,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5024,7 +5024,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5045,7 +5045,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5066,43 +5066,43 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D222" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E222" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>5a-Reductase Type 2</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D223" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E223" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="224">
@@ -5360,40 +5360,40 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>5a-Reductase Type 2</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D236" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E236" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C237" t="n">
+        <v>11</v>
+      </c>
+      <c r="D237" t="n">
         <v>8</v>
-      </c>
-      <c r="D237" t="n">
-        <v>11</v>
       </c>
       <c r="E237" t="n">
         <v>88</v>
@@ -5780,112 +5780,112 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>5a-Reductase Type 2</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D256" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E256" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5a-Reductase Type 2</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D257" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E257" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>5a-Reductase Type 2</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D258" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E258" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>5a-Reductase Type 2</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C259" t="n">
         <v>9</v>
       </c>
       <c r="D259" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E259" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>5a-Reductase Type 2</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C260" t="n">
         <v>9</v>
       </c>
       <c r="D260" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E260" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5894,19 +5894,19 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D261" t="n">
         <v>8</v>
       </c>
       <c r="E261" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -5915,31 +5915,31 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D262" t="n">
         <v>8</v>
       </c>
       <c r="E262" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C263" t="n">
+        <v>9</v>
+      </c>
+      <c r="D263" t="n">
         <v>8</v>
-      </c>
-      <c r="D263" t="n">
-        <v>9</v>
       </c>
       <c r="E263" t="n">
         <v>72</v>
@@ -5948,19 +5948,19 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C264" t="n">
+        <v>9</v>
+      </c>
+      <c r="D264" t="n">
         <v>8</v>
-      </c>
-      <c r="D264" t="n">
-        <v>9</v>
       </c>
       <c r="E264" t="n">
         <v>72</v>
@@ -5969,19 +5969,19 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>Oxidative stress</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C265" t="n">
+        <v>9</v>
+      </c>
+      <c r="D265" t="n">
         <v>8</v>
-      </c>
-      <c r="D265" t="n">
-        <v>9</v>
       </c>
       <c r="E265" t="n">
         <v>72</v>
@@ -5990,19 +5990,19 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C266" t="n">
+        <v>9</v>
+      </c>
+      <c r="D266" t="n">
         <v>8</v>
-      </c>
-      <c r="D266" t="n">
-        <v>9</v>
       </c>
       <c r="E266" t="n">
         <v>72</v>
@@ -6011,43 +6011,22 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Caspase-3</t>
+          <t>5a-Reductase Type 2</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C267" t="n">
+        <v>9</v>
+      </c>
+      <c r="D267" t="n">
         <v>8</v>
-      </c>
-      <c r="D267" t="n">
-        <v>9</v>
       </c>
       <c r="E267" t="n">
         <v>72</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>Caspase-3</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Tretinoin</t>
-        </is>
-      </c>
-      <c r="C268" t="n">
-        <v>8</v>
-      </c>
-      <c r="D268" t="n">
-        <v>8</v>
-      </c>
-      <c r="E268" t="n">
-        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/output/AGA_Gap_Analysis.xlsx
+++ b/output/AGA_Gap_Analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E267"/>
+  <dimension ref="A1:E268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,34 +455,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D2" t="n">
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>2388</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>JAK1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Finasteride</t>
+          <t>Minoxidil</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="E3" t="n">
-        <v>2232</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>2112</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="5">
@@ -539,13 +539,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>1406</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="7">
@@ -563,10 +563,10 @@
         <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>1110</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="8">
@@ -584,10 +584,10 @@
         <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E8" t="n">
-        <v>962</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="9">
@@ -605,10 +605,10 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E9" t="n">
-        <v>962</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="10">
@@ -635,85 +635,85 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dermal papilla cells</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Dutasteride</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="E11" t="n">
-        <v>868</v>
+        <v>880</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Dermal papilla cells</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>868</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E13" t="n">
-        <v>752</v>
+        <v>832</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dermal papilla cells</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>744</v>
+        <v>800</v>
       </c>
     </row>
     <row r="15">
@@ -724,17 +724,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>682</v>
+        <v>744</v>
       </c>
     </row>
     <row r="16">
@@ -752,10 +752,10 @@
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>666</v>
+        <v>720</v>
       </c>
     </row>
     <row r="17">
@@ -773,220 +773,220 @@
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E17" t="n">
-        <v>666</v>
+        <v>720</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>Dermal papilla cells</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dutasteride</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>666</v>
+        <v>682</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dutasteride</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>666</v>
+        <v>650</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dermal papilla cells</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>Dermal papilla cells</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>611</v>
+        <v>620</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>Dermal papilla cells</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>611</v>
+        <v>620</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D23" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>608</v>
+        <v>600</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="D24" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>576</v>
+        <v>600</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E25" t="n">
-        <v>564</v>
+        <v>576</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E26" t="n">
-        <v>564</v>
+        <v>576</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dermal papilla cells</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E27" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="28">
@@ -997,7 +997,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1055,70 +1055,70 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>Dermal papilla cells</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>517</v>
+        <v>558</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dermal papilla cells</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E32" t="n">
-        <v>496</v>
+        <v>550</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D33" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D34" t="n">
         <v>32</v>
       </c>
       <c r="E34" t="n">
-        <v>448</v>
+        <v>480</v>
       </c>
     </row>
     <row r="35">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D35" t="n">
         <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>423</v>
+        <v>450</v>
       </c>
     </row>
     <row r="36">
@@ -1169,34 +1169,34 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D36" t="n">
         <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>423</v>
+        <v>450</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D37" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E37" t="n">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="38">
@@ -1211,97 +1211,97 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D38" t="n">
         <v>16</v>
       </c>
       <c r="E38" t="n">
-        <v>400</v>
+        <v>416</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D39" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E39" t="n">
-        <v>392</v>
+        <v>416</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D40" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E40" t="n">
-        <v>376</v>
+        <v>392</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D41" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E41" t="n">
-        <v>364</v>
+        <v>384</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D42" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E42" t="n">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="43">
@@ -1316,160 +1316,160 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D43" t="n">
         <v>14</v>
       </c>
       <c r="E43" t="n">
-        <v>350</v>
+        <v>364</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D44" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E44" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D45" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E45" t="n">
-        <v>336</v>
+        <v>360</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D46" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E46" t="n">
-        <v>336</v>
+        <v>352</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>5α-Reductase Type II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D47" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E47" t="n">
-        <v>325</v>
+        <v>352</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D48" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E48" t="n">
-        <v>325</v>
+        <v>352</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D49" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E49" t="n">
-        <v>320</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D50" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E50" t="n">
-        <v>320</v>
+        <v>338</v>
       </c>
     </row>
     <row r="51">
@@ -1480,59 +1480,59 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>28</v>
       </c>
       <c r="D51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E51" t="n">
-        <v>308</v>
+        <v>336</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D52" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E52" t="n">
-        <v>304</v>
+        <v>336</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D53" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E53" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54">
@@ -1543,77 +1543,77 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D54" t="n">
         <v>12</v>
       </c>
       <c r="E54" t="n">
-        <v>300</v>
+        <v>312</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D55" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E55" t="n">
-        <v>288</v>
+        <v>312</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D56" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E56" t="n">
-        <v>288</v>
+        <v>308</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D57" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E57" t="n">
         <v>288</v>
@@ -1622,19 +1622,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D58" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E58" t="n">
         <v>288</v>
@@ -1643,19 +1643,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Spironolactone</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D59" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E59" t="n">
         <v>288</v>
@@ -1664,85 +1664,85 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D60" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E60" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>JAK1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D61" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E61" t="n">
-        <v>275</v>
+        <v>288</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Spironolactone</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D62" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E62" t="n">
-        <v>270</v>
+        <v>288</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D63" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E63" t="n">
-        <v>266</v>
+        <v>286</v>
       </c>
     </row>
     <row r="64">
@@ -1753,119 +1753,119 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>28</v>
       </c>
       <c r="D64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E64" t="n">
-        <v>252</v>
+        <v>280</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D65" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E65" t="n">
-        <v>252</v>
+        <v>280</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E66" t="n">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E67" t="n">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D68" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E68" t="n">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D69" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E69" t="n">
         <v>252</v>
@@ -1874,19 +1874,19 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D70" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E70" t="n">
         <v>252</v>
@@ -1895,169 +1895,169 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E71" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D72" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E72" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Hair follicle stem cells</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D73" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E73" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D74" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E74" t="n">
-        <v>240</v>
+        <v>252</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>18</v>
       </c>
       <c r="D75" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E75" t="n">
-        <v>234</v>
+        <v>252</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D76" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E76" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D77" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E77" t="n">
-        <v>228</v>
+        <v>240</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D78" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E78" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="79">
@@ -2068,17 +2068,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D79" t="n">
         <v>9</v>
       </c>
       <c r="E79" t="n">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="80">
@@ -2089,17 +2089,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D80" t="n">
         <v>9</v>
       </c>
       <c r="E80" t="n">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="81">
@@ -2110,338 +2110,338 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D81" t="n">
         <v>9</v>
       </c>
       <c r="E81" t="n">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D82" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E82" t="n">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Hair follicle stem cells</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D83" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E83" t="n">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D84" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E84" t="n">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>18</v>
       </c>
       <c r="D85" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E85" t="n">
-        <v>216</v>
+        <v>234</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D86" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E86" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>5α-Reductase Type II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D87" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E87" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D88" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E88" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D89" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E89" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D90" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E90" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D91" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E91" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D92" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E92" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D93" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E93" t="n">
-        <v>198</v>
+        <v>208</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D94" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E94" t="n">
-        <v>196</v>
+        <v>208</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D95" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E95" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D96" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E96" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2450,55 +2450,55 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D97" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E97" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D98" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E98" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D99" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E99" t="n">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="100">
@@ -2509,86 +2509,86 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>14</v>
       </c>
       <c r="D100" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E100" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D101" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E101" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D102" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E102" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D103" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E103" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2597,139 +2597,139 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D104" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E104" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D105" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E105" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D106" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E106" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D107" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E107" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D108" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E108" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D109" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E109" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D110" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E110" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="111">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D111" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E111" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="112">
@@ -2761,569 +2761,569 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D112" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E112" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D113" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E113" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D114" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E114" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D115" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E115" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>JAK1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Testosterone</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D116" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E116" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D117" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E117" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D118" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E118" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>5α-Reductase Type II</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D119" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E119" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>5α-Reductase Type II</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D120" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E120" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C121" t="n">
         <v>11</v>
       </c>
       <c r="D121" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E121" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D122" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E122" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D123" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E123" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D124" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E124" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D125" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E125" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D126" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E126" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D127" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E127" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D128" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E128" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D129" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E129" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D130" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E130" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D131" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E131" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D132" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E132" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D133" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E133" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Wnt/β-catenin pathway</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D134" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E134" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D135" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E135" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E136" t="n">
-        <v>150</v>
+        <v>162</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D137" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E137" t="n">
-        <v>150</v>
+        <v>162</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C138" t="n">
         <v>18</v>
       </c>
       <c r="D138" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E138" t="n">
-        <v>144</v>
+        <v>162</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3332,118 +3332,118 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D139" t="n">
         <v>16</v>
       </c>
       <c r="E139" t="n">
-        <v>144</v>
+        <v>160</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D140" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E140" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D141" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E141" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Platelet-rich plasma (PRP)</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D142" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E142" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C143" t="n">
         <v>13</v>
       </c>
       <c r="D143" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E143" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D144" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E144" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
     </row>
     <row r="145">
@@ -3454,65 +3454,65 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D145" t="n">
         <v>13</v>
       </c>
       <c r="E145" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D146" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E146" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C147" t="n">
+        <v>11</v>
+      </c>
+      <c r="D147" t="n">
         <v>14</v>
       </c>
-      <c r="D147" t="n">
-        <v>10</v>
-      </c>
       <c r="E147" t="n">
-        <v>140</v>
+        <v>154</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>5α-Reductase Type II</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3521,34 +3521,34 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D148" t="n">
         <v>14</v>
       </c>
       <c r="E148" t="n">
-        <v>140</v>
+        <v>154</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C149" t="n">
+        <v>15</v>
+      </c>
+      <c r="D149" t="n">
         <v>10</v>
       </c>
-      <c r="D149" t="n">
-        <v>14</v>
-      </c>
       <c r="E149" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="150">
@@ -3559,233 +3559,233 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C150" t="n">
         <v>15</v>
       </c>
       <c r="D150" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E150" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D151" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E151" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D152" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E152" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D153" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E153" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>JAK1</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C154" t="n">
         <v>9</v>
       </c>
       <c r="D154" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E154" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>JAK1</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Dihydrotestosterone (DHT)</t>
         </is>
       </c>
       <c r="C155" t="n">
         <v>9</v>
       </c>
       <c r="D155" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E155" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Testosterone</t>
+          <t>Platelet-rich plasma (PRP)</t>
         </is>
       </c>
       <c r="C156" t="n">
         <v>9</v>
       </c>
       <c r="D156" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E156" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D157" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E157" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D158" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E158" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D159" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E159" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D160" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E160" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>5α-Reductase Type II</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3794,19 +3794,19 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D161" t="n">
         <v>13</v>
       </c>
       <c r="E161" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>5α-Reductase Type II</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3815,19 +3815,19 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D162" t="n">
         <v>13</v>
       </c>
       <c r="E162" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3836,19 +3836,19 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D163" t="n">
         <v>13</v>
       </c>
       <c r="E163" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D164" t="n">
         <v>13</v>
       </c>
       <c r="E164" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
     </row>
     <row r="165">
@@ -3874,17 +3874,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C165" t="n">
         <v>14</v>
       </c>
       <c r="D165" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E165" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
     </row>
     <row r="166">
@@ -3895,380 +3895,380 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C166" t="n">
         <v>14</v>
       </c>
       <c r="D166" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E166" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D167" t="n">
         <v>9</v>
       </c>
       <c r="E167" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D168" t="n">
         <v>9</v>
       </c>
       <c r="E168" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D169" t="n">
         <v>9</v>
       </c>
       <c r="E169" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>Wnt/β-catenin signaling pathway</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D170" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E170" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D171" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E171" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D172" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E172" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Bicalutamide</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D173" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E173" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>5α-Reductase Type II</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone (DHT)</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D174" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E174" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>5α-Reductase Type II</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C175" t="n">
         <v>11</v>
       </c>
       <c r="D175" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E175" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling pathway</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D176" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E176" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D177" t="n">
         <v>12</v>
       </c>
       <c r="E177" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C178" t="n">
+        <v>13</v>
+      </c>
+      <c r="D178" t="n">
         <v>10</v>
       </c>
-      <c r="D178" t="n">
-        <v>12</v>
-      </c>
       <c r="E178" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C179" t="n">
+        <v>13</v>
+      </c>
+      <c r="D179" t="n">
         <v>10</v>
       </c>
-      <c r="D179" t="n">
-        <v>12</v>
-      </c>
       <c r="E179" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C180" t="n">
+        <v>13</v>
+      </c>
+      <c r="D180" t="n">
         <v>10</v>
       </c>
-      <c r="D180" t="n">
-        <v>12</v>
-      </c>
       <c r="E180" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C181" t="n">
         <v>13</v>
       </c>
       <c r="D181" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E181" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D182" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E182" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D183" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E183" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4277,40 +4277,40 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D184" t="n">
         <v>9</v>
       </c>
       <c r="E184" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D185" t="n">
         <v>9</v>
       </c>
       <c r="E185" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4319,19 +4319,19 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D186" t="n">
         <v>9</v>
       </c>
       <c r="E186" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4340,19 +4340,19 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D187" t="n">
         <v>9</v>
       </c>
       <c r="E187" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4361,220 +4361,220 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D188" t="n">
         <v>9</v>
       </c>
       <c r="E188" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>JAK1</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C189" t="n">
         <v>9</v>
       </c>
       <c r="D189" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E189" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Bicalutamide</t>
         </is>
       </c>
       <c r="C190" t="n">
         <v>9</v>
       </c>
       <c r="D190" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E190" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D191" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E191" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>5α-Reductase Type II</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D192" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E192" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D193" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E193" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D194" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E194" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D195" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E195" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D196" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E196" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D197" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E197" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Platelet-Rich Plasma (PRP)</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D198" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E198" t="n">
         <v>117</v>
@@ -4583,295 +4583,295 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D199" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E199" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>TGF-β1</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D200" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E200" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D201" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E201" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D202" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E202" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D203" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E203" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D204" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E204" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>Potassium channels</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D205" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E205" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C206" t="n">
         <v>9</v>
       </c>
       <c r="D206" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E206" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C207" t="n">
         <v>9</v>
       </c>
       <c r="D207" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E207" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>JAK1</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C208" t="n">
         <v>9</v>
       </c>
       <c r="D208" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E208" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>JAK1</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Cyclophosphamide</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C209" t="n">
         <v>9</v>
       </c>
       <c r="D209" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E209" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C210" t="n">
         <v>9</v>
       </c>
       <c r="D210" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E210" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TGF-β1</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Platelet-Rich Plasma (PRP)</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D211" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E211" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Potassium channels</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D212" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E212" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="213">
@@ -4886,307 +4886,307 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D213" t="n">
         <v>10</v>
       </c>
       <c r="E213" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5α-Reductase Type II</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D214" t="n">
         <v>10</v>
       </c>
       <c r="E214" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>5α-Reductase Type II</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C215" t="n">
         <v>11</v>
       </c>
       <c r="D215" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E215" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C216" t="n">
         <v>11</v>
       </c>
       <c r="D216" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E216" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C217" t="n">
         <v>11</v>
       </c>
       <c r="D217" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E217" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D218" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E218" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D219" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E219" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D220" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E220" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D221" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E221" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>5-Alpha Reductase Type 2</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D222" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E222" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C223" t="n">
         <v>9</v>
       </c>
       <c r="D223" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E223" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D224" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E224" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>JAK1</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Cyclophosphamide</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D225" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E225" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>JAK1</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D226" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E226" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D227" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E227" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
     <row r="228">
@@ -5204,10 +5204,10 @@
         <v>10</v>
       </c>
       <c r="D228" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E228" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="229">
@@ -5218,332 +5218,332 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C229" t="n">
         <v>10</v>
       </c>
       <c r="D229" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E229" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D230" t="n">
         <v>9</v>
       </c>
       <c r="E230" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D231" t="n">
         <v>9</v>
       </c>
       <c r="E231" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D232" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E232" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>5α-Reductase Type 1</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D233" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E233" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>5α-Reductase Type II</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D234" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E234" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>5α-Reductase Type II</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D235" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E235" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>5α-Reductase Type II</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D236" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E236" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 2</t>
+          <t>5α-Reductase Type II</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C237" t="n">
         <v>11</v>
       </c>
       <c r="D237" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E237" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>5α-Reductase Type II</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D238" t="n">
         <v>9</v>
       </c>
       <c r="E238" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D239" t="n">
         <v>9</v>
       </c>
       <c r="E239" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D240" t="n">
         <v>9</v>
       </c>
       <c r="E240" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D241" t="n">
         <v>9</v>
       </c>
       <c r="E241" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>IL-6</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D242" t="n">
         <v>9</v>
       </c>
       <c r="E242" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C243" t="n">
         <v>9</v>
       </c>
       <c r="D243" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E243" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>JAK1</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C244" t="n">
         <v>9</v>
       </c>
       <c r="D244" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E244" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="245">
@@ -5554,149 +5554,149 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C245" t="n">
         <v>9</v>
       </c>
       <c r="D245" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E245" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Bcl-2</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D246" t="n">
         <v>9</v>
       </c>
       <c r="E246" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D247" t="n">
         <v>9</v>
       </c>
       <c r="E247" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D248" t="n">
         <v>9</v>
       </c>
       <c r="E248" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>TGF-β2</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D249" t="n">
         <v>9</v>
       </c>
       <c r="E249" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C250" t="n">
         <v>9</v>
       </c>
       <c r="D250" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E250" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C251" t="n">
         <v>9</v>
       </c>
       <c r="D251" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E251" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>JAK1</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5708,84 +5708,84 @@
         <v>9</v>
       </c>
       <c r="D252" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E252" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>JAK1</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C253" t="n">
         <v>9</v>
       </c>
       <c r="D253" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E253" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Dihydrotestosterone</t>
         </is>
       </c>
       <c r="C254" t="n">
         <v>9</v>
       </c>
       <c r="D254" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E254" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Ketoconazole</t>
         </is>
       </c>
       <c r="C255" t="n">
         <v>9</v>
       </c>
       <c r="D255" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E255" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Tretinoin</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -5801,12 +5801,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Dihydrotestosterone</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -5822,12 +5822,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Flutamide</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -5843,12 +5843,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>DKK1</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -5864,12 +5864,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>JAK1</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Cyproterone acetate</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -5885,7 +5885,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 1</t>
+          <t>JAK1</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5894,55 +5894,55 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D261" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E261" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>TGF-β2</t>
+          <t>JAK1</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D262" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E262" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>DKK1</t>
+          <t>JAK1</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Cyproterone acetate</t>
         </is>
       </c>
       <c r="C263" t="n">
         <v>9</v>
       </c>
       <c r="D263" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E263" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="264">
@@ -5953,23 +5953,23 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="C264" t="n">
         <v>9</v>
       </c>
       <c r="D264" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E264" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Oxidative stress</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -5981,52 +5981,73 @@
         <v>9</v>
       </c>
       <c r="D265" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E265" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>IL-6</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Flutamide</t>
         </is>
       </c>
       <c r="C266" t="n">
         <v>9</v>
       </c>
       <c r="D266" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E266" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>Bcl-2</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Tretinoin</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C267" t="n">
         <v>9</v>
       </c>
       <c r="D267" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E267" t="n">
-        <v>72</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Bcl-2</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Cyproterone acetate</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>9</v>
+      </c>
+      <c r="D268" t="n">
+        <v>9</v>
+      </c>
+      <c r="E268" t="n">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
